--- a/docs/collections/fujikawa/metadata/data.xlsx
+++ b/docs/collections/fujikawa/metadata/data.xlsx
@@ -10773,7 +10773,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/da3b5a9a-286f-876c-92f0-e4f236e342af</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/fujikawa/document/da3b5a9a-286f-876c-92f0-e4f236e342af</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/medlib/document/521509c3-47cb-a130-8701-c38ecf4a2b38</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/fujikawa/document/521509c3-47cb-a130-8701-c38ecf4a2b38</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
